--- a/products_sku_list.xlsx
+++ b/products_sku_list.xlsx
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>YH502</t>
+          <t>YH504</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
